--- a/Suivi de préparation audit GMP.xlsx
+++ b/Suivi de préparation audit GMP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\0-MYC-TN-2026\11- Audit et préparation\2026\GMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.10.30.100\myc-common\0-MYC-TN-2026\11- Audit et préparation\2026\GMP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291EBCE8-7724-4977-8257-40F7A7C28A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54B9A46-F8EB-4303-809B-AE80E6B6FDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Check-list GMP" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="120">
   <si>
     <t xml:space="preserve">Point à audité </t>
   </si>
@@ -62,9 +62,6 @@
     <t xml:space="preserve">Copie de licence </t>
   </si>
   <si>
-    <t>Chaima</t>
-  </si>
-  <si>
     <t>In progress</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mettre la dernère version codifié de flux de process avec date de mise à jour </t>
-  </si>
-  <si>
-    <t>Saif et Salh</t>
   </si>
   <si>
     <t xml:space="preserve"> 4 Quality policy/objective/manual/system </t>
@@ -95,18 +89,12 @@
 </t>
   </si>
   <si>
-    <t>Naoures</t>
-  </si>
-  <si>
     <t>5 Management review procedure/plan/report/corrective &amp; preventive action record</t>
   </si>
   <si>
     <t>Procédure de management review
 Plan de management review
 Rapport de Management review 2026</t>
-  </si>
-  <si>
-    <t>Sami</t>
   </si>
   <si>
     <t xml:space="preserve"> 6 Document management system </t>
@@ -132,9 +120,6 @@
 Masterlist des documents externe </t>
   </si>
   <si>
-    <t>Faten</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 9 Document change system </t>
   </si>
   <si>
@@ -187,9 +172,6 @@
   </si>
   <si>
     <t>Liste des équipement laboratoire</t>
-  </si>
-  <si>
-    <t>Chaima Q</t>
   </si>
   <si>
     <t>18 Equipment calibration records</t>
@@ -236,9 +218,6 @@
     <t xml:space="preserve">plan de maintenance preventif rempli avec les intervention effectuées </t>
   </si>
   <si>
-    <t>Hammadi</t>
-  </si>
-  <si>
     <t>25 Purified water production, maintenance, verification procedures(bache à eaux)osmoseur</t>
   </si>
   <si>
@@ -258,12 +237,6 @@
     <t xml:space="preserve">Tracabilité e désinfection de l'eau </t>
   </si>
   <si>
-    <t>28 Water physical, chemical and microbiological quality check records: Med control</t>
-  </si>
-  <si>
-    <t>Rapport med control d'analyse d'eau ( chaque mois)</t>
-  </si>
-  <si>
     <t xml:space="preserve">29 Air treatment units maintenance procedures and records </t>
   </si>
   <si>
@@ -271,9 +244,6 @@
 Suivi ( preuve de maintenance) </t>
   </si>
   <si>
-    <t>Hamadi</t>
-  </si>
-  <si>
     <t>30 Air quality check procedures and records</t>
   </si>
   <si>
@@ -296,9 +266,6 @@
     <t xml:space="preserve">Rapport qualité </t>
   </si>
   <si>
-    <t xml:space="preserve">Naoures/Chaima </t>
-  </si>
-  <si>
     <t xml:space="preserve">34 Storage (incoming materials, semi-finished products, finished products) cleaning procedures and records </t>
   </si>
   <si>
@@ -308,16 +275,10 @@
     <t>SOP machines</t>
   </si>
   <si>
-    <t>Saif/Slah</t>
-  </si>
-  <si>
     <t xml:space="preserve">36 Working instructions </t>
   </si>
   <si>
     <t xml:space="preserve">Document 3eme niveau </t>
-  </si>
-  <si>
-    <t>Slah/Saif</t>
   </si>
   <si>
     <t xml:space="preserve">37 Production planning </t>
@@ -333,9 +294,6 @@
 Copie des checklist démarrage rempli </t>
   </si>
   <si>
-    <t>Walid</t>
-  </si>
-  <si>
     <t xml:space="preserve">39 Trial production records </t>
   </si>
   <si>
@@ -361,9 +319,6 @@
   </si>
   <si>
     <t>SOP emballage</t>
-  </si>
-  <si>
-    <t>Seif-Slah</t>
   </si>
   <si>
     <t>44 Batch File (records of traceability)</t>
@@ -449,7 +404,28 @@
 </t>
   </si>
   <si>
-    <t>Saif/Chaima</t>
+    <t>28 Water physical, chemical and microbiological quality check records:Chimitex&amp;eau potable</t>
+  </si>
+  <si>
+    <t>Rapport d'analyse chimitex et eau potable  d'analyse d'eau ( chaque mois)</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>Qualité</t>
+  </si>
+  <si>
+    <t>Département technique</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Supply chain</t>
+  </si>
+  <si>
+    <t>DONE</t>
   </si>
 </sst>
 </file>
@@ -479,7 +455,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,6 +489,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,10 +550,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -581,15 +559,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,17 +853,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.453125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="42.08984375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="19.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -891,14 +873,14 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -909,1066 +891,1068 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+      <c r="E3" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="80" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F5" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="64" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="64" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F8" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F11" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F12" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F13" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F15" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="64" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F21" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="80" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F22" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="80" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F25" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="56.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>59</v>
+      <c r="B26" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F26" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="48" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
+        <v>116</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+      <c r="B28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F30" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F34" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F36" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F37" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>90</v>
+        <v>76</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F39" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F40" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F41" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F42" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F45" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F48" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F50" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F51" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="48" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F53" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="13">
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F54" s="10">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="13">
+      <c r="E55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="10">
         <v>46304</v>
       </c>
     </row>
